--- a/_Drive/Publicacoes/jeff.xlsx
+++ b/_Drive/Publicacoes/jeff.xlsx
@@ -4,7 +4,7 @@
   <fileVersion lastEdited="4" lowestEdited="4" rupBuild="3820"/>
   <workbookPr date1904="0"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView activeTab="0" windowWidth="14400" windowHeight="6300"/>
   </bookViews>
   <sheets>
     <sheet name="jeff.doi" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,62 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="12" count="12">
+  <si>
+    <t>DOI</t>
+  </si>
+  <si>
+    <t>10.1103/physrevb.95.144505</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2019.06.186</t>
+  </si>
+  <si>
+    <t>10.1016/j.ssc.2018.08.014</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-019-00756-6</t>
+  </si>
+  <si>
+    <t>10.1016/j.mtla.2018.11.008</t>
+  </si>
+  <si>
+    <t>10.1016/j.jallcom.2015.11.101</t>
+  </si>
+  <si>
+    <t>10.1016/j.ssc.2008.12.037</t>
+  </si>
+  <si>
+    <t>10.1016/j.ssc.2010.04.036</t>
+  </si>
+  <si>
+    <t>10.1016/j.ssc.2011.07.005</t>
+  </si>
+  <si>
+    <t>10.1088/0953-2048/28/9/095016</t>
+  </si>
+  <si>
+    <t>10.1007/s11669-015-0418-y</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <b val="0"/>
+      <i val="0"/>
+      <u val="none"/>
+      <color rgb="FF000000"/>
+      <name val="Sans"/>
+      <vertAlign val="baseline"/>
+      <sz val="10"/>
+      <strike val="0"/>
+    </font>
+    <font>
+      <b val="1"/>
       <i val="0"/>
       <u val="none"/>
       <color rgb="FF000000"/>
@@ -62,8 +113,12 @@
       <protection locked="1" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
+      <protection locked="1" hidden="0"/>
+    </xf>
+    <xf applyAlignment="1" applyBorder="1" applyFont="1" applyFill="1" applyNumberFormat="1" fontId="1" fillId="0" borderId="0" numFmtId="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="0" shrinkToFit="0" textRotation="0" indent="0"/>
       <protection locked="1" hidden="0"/>
     </xf>
@@ -76,455 +131,439 @@
   <sheetPr>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A65"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="256" style="0" width="9.142307692307693"/>
+    <col min="1" max="1" style="0" width="31.283834134615386" bestFit="1" customWidth="1"/>
+    <col min="2" max="16384" style="0" width="9.142307692307693"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>10.1016/S0921-4534(02)02802-2</t>
-        </is>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10.1063/1.4757003</t>
+          <t>10.1016/S0921-4534(02)02802-2</t>
         </is>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10.1007/s42452-019-1479-z</t>
+          <t>10.1063/1.4757003</t>
         </is>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10.1103/physrevb.95.144505</t>
+          <t>10.1007/s42452-019-1479-z</t>
         </is>
       </c>
     </row>
     <row r="5" spans="1:1">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>10.1016/S0921-4534(01)00106-X</t>
-        </is>
+      <c r="A5" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2019.02.072</t>
+          <t>10.1016/S0921-4534(01)00106-X</t>
         </is>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10.1016/j.physleta.2018.02.018</t>
+          <t>10.1016/j.jallcom.2019.02.072</t>
         </is>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10.1016/S0921-4534(00)00776-0</t>
+          <t>10.1016/j.physleta.2018.02.018</t>
         </is>
       </c>
     </row>
     <row r="9" spans="1:1">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10.1016/j.matlet.2006.04.094</t>
+          <t>10.1016/S0921-4534(00)00776-0</t>
         </is>
       </c>
     </row>
     <row r="10" spans="1:1">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10.1016/j.jallcom.2019.06.186</t>
+          <t>10.1016/j.matlet.2006.04.094</t>
         </is>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>10.1016/j.ssc.2018.08.014</t>
-        </is>
+      <c r="A11" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>10.1016/j.matchemphys.2019.01.008</t>
-        </is>
+      <c r="A12" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:1">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10.1063/1.4821283</t>
+          <t>10.1016/j.matchemphys.2019.01.008</t>
         </is>
       </c>
     </row>
     <row r="14" spans="1:1">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/29/9/095007</t>
+          <t>10.1063/1.4821283</t>
         </is>
       </c>
     </row>
     <row r="15" spans="1:1">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10.1179/1433075x14y.0000000228</t>
+          <t>10.1088/0953-2048/29/9/095007</t>
         </is>
       </c>
     </row>
     <row r="16" spans="1:1">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10.1016/j.ssc.2006.05.006</t>
+          <t>10.1179/1433075x14y.0000000228</t>
         </is>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10.1016/j.ssc.2007.09.028</t>
+          <t>10.1016/j.ssc.2006.05.006</t>
         </is>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.02.058</t>
+          <t>10.1016/j.ssc.2007.09.028</t>
         </is>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevB.81.174532</t>
+          <t>10.1016/j.physc.2004.02.058</t>
         </is>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.177</t>
+          <t>10.1103/PhysRevB.81.174532</t>
         </is>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevB.74.184526</t>
+          <t>10.1016/j.physc.2004.03.177</t>
         </is>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10.1016/j.matchemphys.2017.03.037</t>
+          <t>10.1103/PhysRevB.74.184526</t>
         </is>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10.1016/j.physleta.2015.02.002</t>
+          <t>10.1016/j.matchemphys.2017.03.037</t>
         </is>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.12.005</t>
+          <t>10.1016/j.physleta.2015.02.002</t>
         </is>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10.1103/physrevb.98.045126</t>
+          <t>10.1016/j.physc.2004.12.005</t>
         </is>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10.1016/j.ceramint.2020.11.013</t>
+          <t>10.1103/physrevb.98.045126</t>
         </is>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10.1016/S0921-4534(00)01261-2</t>
+          <t>10.1016/j.ceramint.2020.11.013</t>
         </is>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10.1016/j.physleta.2015.07.018</t>
+          <t>10.1016/S0921-4534(00)01261-2</t>
         </is>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.02.173</t>
+          <t>10.1016/j.physleta.2015.07.018</t>
         </is>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/24/7/075017</t>
+          <t>10.1016/j.physc.2004.02.173</t>
         </is>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10.1103/physrevb.87.174502</t>
+          <t>10.1088/0953-2048/24/7/075017</t>
         </is>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="inlineStr">
         <is>
-          <t>10.1007/s11669-019-00756-6</t>
+          <t>10.1103/physrevb.87.174502</t>
         </is>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>10.1016/j.physc.2005.03.010</t>
-        </is>
+      <c r="A33" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="inlineStr">
         <is>
-          <t>10.1016/j.mtla.2018.11.008</t>
+          <t>10.1016/j.physc.2005.03.010</t>
         </is>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>10.1016/j.jallcom.2015.11.101</t>
-        </is>
+      <c r="A35" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>10.1103/physrevresearch.2.022001</t>
-        </is>
+      <c r="A36" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="inlineStr">
         <is>
-          <t>10.1103/PhysRevB.95.094505</t>
+          <t>10.1103/physrevresearch.2.022001</t>
         </is>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="inlineStr">
         <is>
-          <t>10.1016/0167-577X(92)90116-2</t>
+          <t>10.1103/PhysRevB.95.094505</t>
         </is>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="inlineStr">
         <is>
-          <t>10.1063/1.4730611</t>
+          <t>10.1016/0167-577X(92)90116-2</t>
         </is>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>10.1016/j.ceramint.2014.08.050</t>
+          <t>10.1063/1.4730611</t>
         </is>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>10.1016/S0921-4534(01)00066-1</t>
+          <t>10.1016/j.ceramint.2014.08.050</t>
         </is>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>10.1016/S0921-4534(03)00963-8</t>
+          <t>10.1016/S0921-4534(01)00066-1</t>
         </is>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.228</t>
+          <t>10.1016/S0921-4534(03)00963-8</t>
         </is>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2009.02.005</t>
+          <t>10.1016/j.physc.2004.03.228</t>
         </is>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>10.5772/48625</t>
+          <t>10.1016/j.physc.2009.02.005</t>
         </is>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>10.1016/j.ssc.2008.12.037</t>
+          <t>10.5772/48625</t>
         </is>
       </c>
     </row>
     <row r="47" spans="1:1">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>10.1103/PhysRevLett.122.147001</t>
-        </is>
+      <c r="A47" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10.1016/0167-577X(94)90065-5</t>
+          <t>10.1103/PhysRevLett.122.147001</t>
         </is>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10.1016/j.ssc.2010.04.036</t>
+          <t>10.1016/0167-577X(94)90065-5</t>
         </is>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>10.1016/j.ssc.2011.07.005</t>
-        </is>
+      <c r="A50" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>10.1103/PhysRevB.96.014507</t>
-        </is>
+      <c r="A51" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10.1103/physrevmaterials.1.044803</t>
+          <t>10.1103/PhysRevB.96.014507</t>
         </is>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10.2478/s13536-012-0013-4</t>
+          <t>10.1103/physrevmaterials.1.044803</t>
         </is>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10.1016/j.matlet.2004.08.007</t>
+          <t>10.2478/s13536-012-0013-4</t>
         </is>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/28/9/095016</t>
+          <t>10.1016/j.matlet.2004.08.007</t>
         </is>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>10.1007/s11669-015-0418-y</t>
-        </is>
+      <c r="A56" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>10.1007/s13538-015-0307-1</t>
-        </is>
+      <c r="A57" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10.1016/j.physc.2004.03.176</t>
+          <t>10.1007/s13538-015-0307-1</t>
         </is>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/27/3/035005</t>
+          <t>10.1016/j.physc.2004.03.176</t>
         </is>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/27/3/035004</t>
+          <t>10.1088/0953-2048/27/3/035005</t>
         </is>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/24/9/095007</t>
+          <t>10.1088/0953-2048/27/3/035004</t>
         </is>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10.1016/j.physb.2016.04.030</t>
+          <t>10.1088/0953-2048/24/9/095007</t>
         </is>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10.1088/0953-2048/25/4/045010</t>
+          <t>10.1016/j.physb.2016.04.030</t>
         </is>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="inlineStr">
+        <is>
+          <t>10.1088/0953-2048/25/4/045010</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="inlineStr">
         <is>
           <t>10.1016/j.physc.2008.11.003</t>
         </is>
